--- a/training_survey_templates/013_teacher_professional_development_and_evaluation_survey--training_survey_templates.xlsx
+++ b/training_survey_templates/013_teacher_professional_development_and_evaluation_survey--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>training_survey_templates_1</t>
+          <t>training_survey_templates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Training Survey Templates</t>
+          <t>What are the training survey templates used for?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>What is the form ID?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>teacher_professional_development_and_evaluation_survey_description</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description of the teacher professional development and evaluation survey</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Which tool has been assigned to you?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What category does the tool belong to?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>What is the output file format?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teacher_professional_development_and_evaluation_survey_description</t>
+          <t>teacher_professional_development_and_evaluation_survey_description_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Which tool is assigned to you?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,35 +704,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>teacher_professional_development_and_evaluation_survey_description_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Teacher Professional Development And Evaluation Survey Description 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,39 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>teacher_professional_development_and_evaluation_survey_description</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Form Id</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -825,9 +802,9 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,34 +827,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>training_survey_templates_1_choices</t>
+          <t>training_survey_templates_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes,_for_training_and_evaluation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes, for training and evaluation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>training_survey_templates_1_choices</t>
+          <t>training_survey_templates_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no,_only_for_evaluation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, only for evaluation</t>
         </is>
       </c>
     </row>
@@ -969,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1003,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1020,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1037,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
